--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_5_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_5_7.xlsx
@@ -513,221 +513,221 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_0</t>
+          <t>model_5_7_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9986898672510701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5044578366462801</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9875934426499773</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9938334900379245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9934498380468413</v>
       </c>
       <c r="G2" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0007777513945526741</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2941752344736163</v>
       </c>
       <c r="I2" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002318204876167026</v>
       </c>
       <c r="J2" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002540295428696884</v>
       </c>
       <c r="K2" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.002429250152431955</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.008169242868776726</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02788819453734275</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003060939016538</v>
+        <v>1.031443185974317</v>
       </c>
       <c r="O2" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02907545271531869</v>
       </c>
       <c r="P2" t="n">
-        <v>68.97712837915313</v>
+        <v>64.3182072582556</v>
       </c>
       <c r="Q2" t="n">
-        <v>99.44902400085815</v>
+        <v>94.79010287996061</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_22</t>
+          <t>model_5_7_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9987432850736571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5037357648391381</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9879861288010344</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9941368139943659</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9937172498991657</v>
       </c>
       <c r="G3" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.000746040267535264</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2946038874902137</v>
       </c>
       <c r="I3" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002244830214324818</v>
       </c>
       <c r="J3" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002415341043688</v>
       </c>
       <c r="K3" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.002330075462146972</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007992562129353835</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02731373770715506</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003060939016538</v>
+        <v>1.030161158232231</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02847654006858033</v>
       </c>
       <c r="P3" t="n">
-        <v>68.97712837915313</v>
+        <v>64.40146196257592</v>
       </c>
       <c r="Q3" t="n">
-        <v>99.44902400085815</v>
+        <v>94.87335758428094</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_21</t>
+          <t>model_5_7_20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9988346552505266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5031350379348041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9887854788290659</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9945977289567072</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9941745478734901</v>
       </c>
       <c r="G4" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0006917989835594117</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2949605049306774</v>
       </c>
       <c r="I4" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002095469107898021</v>
       </c>
       <c r="J4" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002225467001635969</v>
       </c>
       <c r="K4" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.002160477949630673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007710642773633337</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02630207184917971</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003060939016538</v>
+        <v>1.027968273987361</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02742180550059394</v>
       </c>
       <c r="P4" t="n">
-        <v>68.97712837915313</v>
+        <v>64.55243026146343</v>
       </c>
       <c r="Q4" t="n">
-        <v>99.44902400085815</v>
+        <v>95.02432588316844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_20</t>
+          <t>model_5_7_22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.998807359330224</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5031240017620138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9884951058145077</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9944832338317218</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9940378100382576</v>
       </c>
       <c r="G5" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0007080030209733998</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2949670564795835</v>
       </c>
       <c r="I5" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002149726233324902</v>
       </c>
       <c r="J5" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002272633299006312</v>
       </c>
       <c r="K5" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.002211189734996784</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007787428438123178</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.026608326158806</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003060939016538</v>
+        <v>1.028623376074624</v>
       </c>
       <c r="O5" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02774109769021484</v>
       </c>
       <c r="P5" t="n">
-        <v>68.97712837915313</v>
+        <v>64.50612439473615</v>
       </c>
       <c r="Q5" t="n">
-        <v>99.44902400085815</v>
+        <v>94.97802001644116</v>
       </c>
     </row>
     <row r="6">
@@ -737,437 +737,437 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9988451127957009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5030508037103081</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9888856750948938</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9946466777104808</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9942269325566839</v>
       </c>
       <c r="G6" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0006855909330015405</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2950105100050673</v>
       </c>
       <c r="I6" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002076747115530369</v>
       </c>
       <c r="J6" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002205302549422938</v>
       </c>
       <c r="K6" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.00214105010944236</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007669333718278623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02618379141762209</v>
       </c>
       <c r="N6" t="n">
-        <v>1.003060939016538</v>
+        <v>1.027717292903179</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02729848962619067</v>
       </c>
       <c r="P6" t="n">
-        <v>68.97712837915313</v>
+        <v>64.57045883135679</v>
       </c>
       <c r="Q6" t="n">
-        <v>99.44902400085815</v>
+        <v>95.0423544530618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_18</t>
+          <t>model_5_7_21</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.998824387419793</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5029535078557849</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9886468802201223</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9945680464548837</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9941231745490888</v>
       </c>
       <c r="G7" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0006978944114301206</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2950682690272743</v>
       </c>
       <c r="I7" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.002121366700761075</v>
       </c>
       <c r="J7" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002237694716203565</v>
       </c>
       <c r="K7" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.00217953070848232</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007748932049899186</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02641769125851312</v>
       </c>
       <c r="N7" t="n">
-        <v>1.003060939016538</v>
+        <v>1.028214701924969</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02754234706754785</v>
       </c>
       <c r="P7" t="n">
-        <v>68.97712837915313</v>
+        <v>64.53488547933514</v>
       </c>
       <c r="Q7" t="n">
-        <v>99.44902400085815</v>
+        <v>95.00678110104016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_17</t>
+          <t>model_5_7_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9989057819154524</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5026404300832095</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9894589618804897</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9949335539267398</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9945307459355011</v>
       </c>
       <c r="G8" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0006495751227475253</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2952541255173307</v>
       </c>
       <c r="I8" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001969626648158483</v>
       </c>
       <c r="J8" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.002087123815382709</v>
       </c>
       <c r="K8" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.002028375231770596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.007492694490782073</v>
       </c>
       <c r="M8" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02548676367739783</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003060939016538</v>
+        <v>1.026261234029142</v>
       </c>
       <c r="O8" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02657178797201872</v>
       </c>
       <c r="P8" t="n">
-        <v>68.97712837915313</v>
+        <v>64.67838413222634</v>
       </c>
       <c r="Q8" t="n">
-        <v>99.44902400085815</v>
+        <v>95.15027975393136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_16</t>
+          <t>model_5_7_15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9991076672195265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5018324081424986</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9916887030696802</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9957457331679302</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9955435190383396</v>
       </c>
       <c r="G9" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.000529727285258119</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.295733802246067</v>
       </c>
       <c r="I9" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001552992383588517</v>
       </c>
       <c r="J9" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001752546359679671</v>
       </c>
       <c r="K9" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.001652769371634094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006888742066755405</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02301580511861619</v>
       </c>
       <c r="N9" t="n">
-        <v>1.003060939016538</v>
+        <v>1.021415986731364</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02399563559180038</v>
       </c>
       <c r="P9" t="n">
-        <v>68.97712837915313</v>
+        <v>65.08629647992859</v>
       </c>
       <c r="Q9" t="n">
-        <v>99.44902400085815</v>
+        <v>95.55819210163361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_15</t>
+          <t>model_5_7_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9990721054066093</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5015736326079274</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.991105503257016</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.995687663034219</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9953643521936125</v>
       </c>
       <c r="G10" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0005508383135960803</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2958874225819095</v>
       </c>
       <c r="I10" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001661965131737338</v>
       </c>
       <c r="J10" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001776468366798412</v>
       </c>
       <c r="K10" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.001719216749267875</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006931929209941987</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02346994489972399</v>
       </c>
       <c r="N10" t="n">
-        <v>1.003060939016538</v>
+        <v>1.022269470241377</v>
       </c>
       <c r="O10" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.0244691090435889</v>
       </c>
       <c r="P10" t="n">
-        <v>68.97712837915313</v>
+        <v>65.00813846724643</v>
       </c>
       <c r="Q10" t="n">
-        <v>99.44902400085815</v>
+        <v>95.48003408895144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_14</t>
+          <t>model_5_7_17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.999047718751279</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5010830178099477</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9906553143614838</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9956713508880251</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9952418842926426</v>
       </c>
       <c r="G11" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0005653152856488177</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.296178672719446</v>
       </c>
       <c r="I11" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001746084365089121</v>
       </c>
       <c r="J11" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001783188159787237</v>
       </c>
       <c r="K11" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.001764636262438179</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006983417628289883</v>
       </c>
       <c r="M11" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02377635980651407</v>
       </c>
       <c r="N11" t="n">
-        <v>1.003060939016538</v>
+        <v>1.022854749969305</v>
       </c>
       <c r="O11" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02478856866732732</v>
       </c>
       <c r="P11" t="n">
-        <v>68.97712837915313</v>
+        <v>64.95625390952074</v>
       </c>
       <c r="Q11" t="n">
-        <v>99.44902400085815</v>
+        <v>95.42814953122576</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_13</t>
+          <t>model_5_7_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9992295624285829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.5000065179859801</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.99262226082736</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9964203109708498</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9961533450178303</v>
       </c>
       <c r="G12" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0004573650235633505</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2968177295173242</v>
       </c>
       <c r="I12" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001378554134122553</v>
       </c>
       <c r="J12" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001474653853286926</v>
       </c>
       <c r="K12" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.00142660399370474</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006405411941956934</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02138609416334246</v>
       </c>
       <c r="N12" t="n">
-        <v>1.003060939016538</v>
+        <v>1.018490501714012</v>
       </c>
       <c r="O12" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.0222965444671939</v>
       </c>
       <c r="P12" t="n">
-        <v>68.97712837915313</v>
+        <v>65.38005749448274</v>
       </c>
       <c r="Q12" t="n">
-        <v>99.44902400085815</v>
+        <v>95.85195311618776</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_23</t>
+          <t>model_5_7_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9992586888187432</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4993187369306198</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9928057554520104</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9965995125134454</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9962990956239243</v>
       </c>
       <c r="G13" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0004400743401696526</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2972260260623807</v>
       </c>
       <c r="I13" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001344267577295077</v>
       </c>
       <c r="J13" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001400831729870146</v>
       </c>
       <c r="K13" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.001372549653582611</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006283299688202927</v>
       </c>
       <c r="M13" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.02097794890282776</v>
       </c>
       <c r="N13" t="n">
-        <v>1.003060939016538</v>
+        <v>1.017791468350162</v>
       </c>
       <c r="O13" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.02187102361796193</v>
       </c>
       <c r="P13" t="n">
-        <v>68.97712837915313</v>
+        <v>65.45713378078443</v>
       </c>
       <c r="Q13" t="n">
-        <v>99.44902400085815</v>
+        <v>95.92902940248945</v>
       </c>
     </row>
     <row r="14">
@@ -1177,492 +1177,492 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9994173489994519</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4976155168931004</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9943071339489521</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9973502958908989</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9970942769155874</v>
       </c>
       <c r="G14" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0003458868031380708</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2982371310519268</v>
       </c>
       <c r="I14" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.001063730208677172</v>
       </c>
       <c r="J14" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.001091546316659727</v>
       </c>
       <c r="K14" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.001077641789044678</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.005694836790661451</v>
       </c>
       <c r="M14" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01859803223833292</v>
       </c>
       <c r="N14" t="n">
-        <v>1.003060939016538</v>
+        <v>1.013983624013155</v>
       </c>
       <c r="O14" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01938978897395288</v>
       </c>
       <c r="P14" t="n">
-        <v>68.97712837915313</v>
+        <v>65.93879798999015</v>
       </c>
       <c r="Q14" t="n">
-        <v>99.44902400085815</v>
+        <v>96.41069361169517</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_10</t>
+          <t>model_5_7_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9995842411261978</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.494922208299078</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9958747192100911</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9981490664633539</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9979328069548645</v>
       </c>
       <c r="G15" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.000246812427337182</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.2998359953782118</v>
       </c>
       <c r="I15" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0007708218946577918</v>
       </c>
       <c r="J15" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0007624925656296777</v>
       </c>
       <c r="K15" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0007666572301437348</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.004999476420001258</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01571026503077469</v>
       </c>
       <c r="N15" t="n">
-        <v>1.003060939016538</v>
+        <v>1.009978212971252</v>
       </c>
       <c r="O15" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01637908353786668</v>
       </c>
       <c r="P15" t="n">
-        <v>68.97712837915313</v>
+        <v>66.61376382664477</v>
       </c>
       <c r="Q15" t="n">
-        <v>99.44902400085815</v>
+        <v>97.08565944834979</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_9</t>
+          <t>model_5_7_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9996396045351055</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.494041052535486</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9962147568704994</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9984937908166489</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9982099598197441</v>
       </c>
       <c r="G16" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0002139463162348356</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.300359087503427</v>
       </c>
       <c r="I16" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0007072847714897951</v>
       </c>
       <c r="J16" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0006204832760604564</v>
       </c>
       <c r="K16" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0006638699030409132</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.004620874258470402</v>
       </c>
       <c r="M16" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01462690384992106</v>
       </c>
       <c r="N16" t="n">
-        <v>1.003060939016538</v>
+        <v>1.008649491157469</v>
       </c>
       <c r="O16" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01524960142867731</v>
       </c>
       <c r="P16" t="n">
-        <v>68.97712837915313</v>
+        <v>66.89957086625691</v>
       </c>
       <c r="Q16" t="n">
-        <v>99.44902400085815</v>
+        <v>97.37146648796192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_8</t>
+          <t>model_5_7_3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998204314749356</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4921561601431409</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9992516253229273</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9995876688462907</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9995824720243734</v>
       </c>
       <c r="G17" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001065996334345852</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3014780410506348</v>
       </c>
       <c r="I17" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001398361992488374</v>
       </c>
       <c r="J17" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0001698599290877584</v>
       </c>
       <c r="K17" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001548480641682979</v>
       </c>
       <c r="L17" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.005975653494477793</v>
       </c>
       <c r="M17" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01032470984747684</v>
       </c>
       <c r="N17" t="n">
-        <v>1.003060939016538</v>
+        <v>1.004309644601546</v>
       </c>
       <c r="O17" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01076425412077972</v>
       </c>
       <c r="P17" t="n">
-        <v>68.97712837915313</v>
+        <v>68.29286096987678</v>
       </c>
       <c r="Q17" t="n">
-        <v>99.44902400085815</v>
+        <v>98.7647565915818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_7</t>
+          <t>model_5_7_0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9997806912191766</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4916694723474561</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9993616044492351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9999966818156339</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.999837354018964</v>
       </c>
       <c r="G18" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001301911659428535</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3017669599499714</v>
       </c>
       <c r="I18" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001192862481471496</v>
       </c>
       <c r="J18" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>1.36692693737859e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>6.032030613131587e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.003460064020522503</v>
       </c>
       <c r="M18" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01141013435253299</v>
       </c>
       <c r="N18" t="n">
-        <v>1.003060939016538</v>
+        <v>1.005263410739762</v>
       </c>
       <c r="O18" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01189588739415459</v>
       </c>
       <c r="P18" t="n">
-        <v>68.97712837915313</v>
+        <v>67.89301336078599</v>
       </c>
       <c r="Q18" t="n">
-        <v>99.44902400085815</v>
+        <v>98.364908982491</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_6</t>
+          <t>model_5_7_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9999102220336851</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4915484292102624</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9991070626996158</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9997236799906699</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9996215934682591</v>
       </c>
       <c r="G19" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>5.329607901074588e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3018388163850008</v>
       </c>
       <c r="I19" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001668481872498036</v>
       </c>
       <c r="J19" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0001138301017716179</v>
       </c>
       <c r="K19" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001403391445107107</v>
       </c>
       <c r="L19" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.003305559056158943</v>
       </c>
       <c r="M19" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.007300416358725431</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003060939016538</v>
+        <v>1.002154671191558</v>
       </c>
       <c r="O19" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.007611210197061583</v>
       </c>
       <c r="P19" t="n">
-        <v>68.97712837915313</v>
+        <v>69.67929558804964</v>
       </c>
       <c r="Q19" t="n">
-        <v>99.44902400085815</v>
+        <v>100.1511912097547</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_5</t>
+          <t>model_5_7_4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998952472200592</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4912993386569545</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9990548358682322</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9996825994838829</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9995856213372702</v>
       </c>
       <c r="G20" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>6.218577525733408e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.301986687297596</v>
       </c>
       <c r="I20" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001766069375432523</v>
       </c>
       <c r="J20" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0001307532275333772</v>
       </c>
       <c r="K20" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001536800825383147</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.003826567986130386</v>
       </c>
       <c r="M20" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.00788579579099878</v>
       </c>
       <c r="N20" t="n">
-        <v>1.003060939016538</v>
+        <v>1.00251406671858</v>
       </c>
       <c r="O20" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.008221510443669285</v>
       </c>
       <c r="P20" t="n">
-        <v>68.97712837915313</v>
+        <v>69.37076855597101</v>
       </c>
       <c r="Q20" t="n">
-        <v>99.44902400085815</v>
+        <v>99.84266417767603</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_4</t>
+          <t>model_5_7_9</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9997397022179082</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4912104069106188</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9970256671162054</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9990343727336002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9987144318577587</v>
       </c>
       <c r="G21" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001545240077284198</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3020394810238723</v>
       </c>
       <c r="I21" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0005557636014590093</v>
       </c>
       <c r="J21" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0003977904107423007</v>
       </c>
       <c r="K21" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.000476777006100655</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.004010238520447959</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.0124307685896094</v>
       </c>
       <c r="N21" t="n">
-        <v>1.003060939016538</v>
+        <v>1.006247146770203</v>
       </c>
       <c r="O21" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01295997214370747</v>
       </c>
       <c r="P21" t="n">
-        <v>68.97712837915313</v>
+        <v>67.55032216774052</v>
       </c>
       <c r="Q21" t="n">
-        <v>99.44902400085815</v>
+        <v>98.02221778944553</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_3</t>
+          <t>model_5_7_1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998106763232836</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4905246458152451</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9992280060945667</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9997626465903852</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9996736996602257</v>
       </c>
       <c r="G22" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001123907128558819</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.302446578433423</v>
       </c>
       <c r="I22" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001442495275245262</v>
       </c>
       <c r="J22" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>9.777780059357037e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001210145880061906</v>
       </c>
       <c r="L22" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.006170650275170265</v>
       </c>
       <c r="M22" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01060144862063114</v>
       </c>
       <c r="N22" t="n">
-        <v>1.003060939016538</v>
+        <v>1.004543768241194</v>
       </c>
       <c r="O22" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01105277423643543</v>
       </c>
       <c r="P22" t="n">
-        <v>68.97712837915313</v>
+        <v>68.18705849951147</v>
       </c>
       <c r="Q22" t="n">
-        <v>99.44902400085815</v>
+        <v>98.65895412121648</v>
       </c>
     </row>
     <row r="23">
@@ -1672,217 +1672,217 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998394179799668</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4901260218637818</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9992826772076345</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9997897482696373</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9997025307130891</v>
       </c>
       <c r="G23" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>9.532842387377114e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3026832188306697</v>
       </c>
       <c r="I23" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0001340340553896185</v>
       </c>
       <c r="J23" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>8.661325657473832e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001103220524530161</v>
       </c>
       <c r="L23" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.005724558662382084</v>
       </c>
       <c r="M23" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.009763627598068822</v>
       </c>
       <c r="N23" t="n">
-        <v>1.003060939016538</v>
+        <v>1.003853968480797</v>
       </c>
       <c r="O23" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01017928543841402</v>
       </c>
       <c r="P23" t="n">
-        <v>68.97712837915313</v>
+        <v>68.51636506993233</v>
       </c>
       <c r="Q23" t="n">
-        <v>99.44902400085815</v>
+        <v>98.98826069163735</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_1</t>
+          <t>model_5_7_6</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998976198500449</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4887536536718348</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9986199341292178</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9997535539434792</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9995154710812968</v>
       </c>
       <c r="G24" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>6.077727960553833e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3034979158726285</v>
       </c>
       <c r="I24" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0002578697168617269</v>
       </c>
       <c r="J24" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0001015235189192053</v>
       </c>
       <c r="K24" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0001796966178904661</v>
       </c>
       <c r="L24" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.002747200936731426</v>
       </c>
       <c r="M24" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.007795978425158598</v>
       </c>
       <c r="N24" t="n">
-        <v>1.003060939016538</v>
+        <v>1.002457123598923</v>
       </c>
       <c r="O24" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.008127869366617708</v>
       </c>
       <c r="P24" t="n">
-        <v>68.97712837915313</v>
+        <v>69.41658905906061</v>
       </c>
       <c r="Q24" t="n">
-        <v>99.44902400085815</v>
+        <v>99.88848468076563</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_11</t>
+          <t>model_5_7_7</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998295277831569</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.4883891325077824</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9978129334166335</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9994898536368081</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9991657218815829</v>
       </c>
       <c r="G25" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001011996719344055</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3037143113821044</v>
       </c>
       <c r="I25" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0004086603781388915</v>
       </c>
       <c r="J25" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0002101549308041167</v>
       </c>
       <c r="K25" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0003094076544715041</v>
       </c>
       <c r="L25" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.003218489632004656</v>
       </c>
       <c r="M25" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01005980476621716</v>
       </c>
       <c r="N25" t="n">
-        <v>1.003060939016538</v>
+        <v>1.004091333204234</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.0104880714817817</v>
       </c>
       <c r="P25" t="n">
-        <v>68.97712837915313</v>
+        <v>68.3968300857421</v>
       </c>
       <c r="Q25" t="n">
-        <v>99.44902400085815</v>
+        <v>98.86872570744711</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_5_7_24</t>
+          <t>model_5_7_8</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9998724608743109</v>
+        <v>0.9998107234075907</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4272465221535103</v>
+        <v>0.488163679821446</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999922489592626</v>
+        <v>0.9974473539893171</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999542735813203</v>
+        <v>0.9994842678411396</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999716185066152</v>
+        <v>0.9990705254536987</v>
       </c>
       <c r="G26" t="n">
-        <v>7.571273441236839e-05</v>
+        <v>0.0001123627615772125</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3400112061116413</v>
+        <v>0.3038481498357626</v>
       </c>
       <c r="I26" t="n">
-        <v>5.321689589534663e-06</v>
+        <v>0.0004769700620521149</v>
       </c>
       <c r="J26" t="n">
-        <v>3.734893926337591e-05</v>
+        <v>0.0002124560008241582</v>
       </c>
       <c r="K26" t="n">
-        <v>2.133531442645529e-05</v>
+        <v>0.0003447130314381366</v>
       </c>
       <c r="L26" t="n">
-        <v>0.003274461705004662</v>
+        <v>0.003223507726884201</v>
       </c>
       <c r="M26" t="n">
-        <v>0.008701306477326747</v>
+        <v>0.01060013026227567</v>
       </c>
       <c r="N26" t="n">
-        <v>1.003060939016538</v>
+        <v>1.004542638217823</v>
       </c>
       <c r="O26" t="n">
-        <v>0.009071739108254078</v>
+        <v>0.01105139975283539</v>
       </c>
       <c r="P26" t="n">
-        <v>68.97712837915313</v>
+        <v>68.18755595618276</v>
       </c>
       <c r="Q26" t="n">
-        <v>99.44902400085815</v>
+        <v>98.65945157788778</v>
       </c>
     </row>
   </sheetData>
